--- a/artfynd/A 20276-2024 artfynd.xlsx
+++ b/artfynd/A 20276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126196971</v>
       </c>
       <c r="B2" t="n">
-        <v>101647</v>
+        <v>101649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20276-2024 artfynd.xlsx
+++ b/artfynd/A 20276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126196971</v>
       </c>
       <c r="B2" t="n">
-        <v>101649</v>
+        <v>101651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20276-2024 artfynd.xlsx
+++ b/artfynd/A 20276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126196971</v>
       </c>
       <c r="B2" t="n">
-        <v>101651</v>
+        <v>101655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20276-2024 artfynd.xlsx
+++ b/artfynd/A 20276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126196971</v>
       </c>
       <c r="B2" t="n">
-        <v>101655</v>
+        <v>101658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20276-2024 artfynd.xlsx
+++ b/artfynd/A 20276-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126196971</v>
       </c>
       <c r="B2" t="n">
-        <v>101658</v>
+        <v>101667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
